--- a/441-rc---tdduipatient-birthdate/ig/StructureDefinition-tddui-entry-date-origin.xlsx
+++ b/441-rc---tdduipatient-birthdate/ig/StructureDefinition-tddui-entry-date-origin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:28:52+00:00</t>
+    <t>2026-02-26T17:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
